--- a/data/trans_orig/P33B3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023</t>
+          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>23892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>49515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34695</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74760</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>320041</t>
+          <t>318974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>365688</t>
+          <t>366681</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>257136</t>
+          <t>258105</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289153</t>
+          <t>289138</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589623</t>
+          <t>589268</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>646136</t>
+          <t>646309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21486</t>
+          <t>22804</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>30454</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>18584</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44092</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29416</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>29884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62484</t>
+          <t>64500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36038</t>
+          <t>35595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80830</t>
+          <t>81436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81974</t>
+          <t>81848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136896</t>
+          <t>138217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>326647</t>
+          <t>324638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>366360</t>
+          <t>365009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>377035</t>
+          <t>375596</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>442250</t>
+          <t>445859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>717570</t>
+          <t>716816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>796588</t>
+          <t>799072</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27649</t>
+          <t>26652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53258</t>
+          <t>51739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49390</t>
+          <t>49771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62149</t>
+          <t>62288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95172</t>
+          <t>93515</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27274</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>53710</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27181</t>
+          <t>26769</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46286</t>
+          <t>45397</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>93281</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92197</t>
+          <t>91729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100725</t>
+          <t>99409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132566</t>
+          <t>129838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167142</t>
+          <t>167679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212057</t>
+          <t>211800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>359634</t>
+          <t>361403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403825</t>
+          <t>404340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>333642</t>
+          <t>334945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>369864</t>
+          <t>371475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706204</t>
+          <t>708007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763334</t>
+          <t>765794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76855</t>
+          <t>76569</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53142</t>
+          <t>52854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85977</t>
+          <t>84213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69974</t>
+          <t>71801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148867</t>
+          <t>150374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88366</t>
+          <t>88384</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70505</t>
+          <t>70494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101762</t>
+          <t>102697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83084</t>
+          <t>89312</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178962</t>
+          <t>179561</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>49513</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169235</t>
+          <t>169559</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121038</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160942</t>
+          <t>162447</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>146682</t>
+          <t>160246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>314212</t>
+          <t>316077</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>566823</t>
+          <t>566234</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>788846</t>
+          <t>788207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>392277</t>
+          <t>391346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>463209</t>
+          <t>465847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>972997</t>
+          <t>969011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1300128</t>
+          <t>1274402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76041</t>
+          <t>74503</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66882</t>
+          <t>66204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>92641</t>
+          <t>91290</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>119136</t>
+          <t>121151</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>156230</t>
+          <t>157851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28603</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50262</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75340</t>
+          <t>76384</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101372</t>
+          <t>102174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111122</t>
+          <t>111394</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143190</t>
+          <t>145374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101174</t>
+          <t>102344</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>137194</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119340</t>
+          <t>120686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148119</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230193</t>
+          <t>230074</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>276046</t>
+          <t>274915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>322129</t>
+          <t>321644</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>364714</t>
+          <t>364865</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>228988</t>
+          <t>229466</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>263504</t>
+          <t>262574</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>561664</t>
+          <t>561381</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>616908</t>
+          <t>617809</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>34435</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23493</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>101699</t>
+          <t>103731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>56376</t>
+          <t>58672</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145722</t>
+          <t>145698</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22297</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95676</t>
+          <t>95002</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>47698</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>120030</t>
+          <t>119146</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73705</t>
+          <t>73021</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100664</t>
+          <t>97850</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>48378</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>163330</t>
+          <t>164516</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100926</t>
+          <t>105230</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>248433</t>
+          <t>250047</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>192557</t>
+          <t>194864</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>223568</t>
+          <t>224463</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>255653</t>
+          <t>253703</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>512468</t>
+          <t>497798</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>473735</t>
+          <t>474333</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>766440</t>
+          <t>765408</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>38096</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>56443</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>72469</t>
+          <t>72480</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>95986</t>
+          <t>96903</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>116629</t>
+          <t>116287</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>145983</t>
+          <t>146264</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>54428</t>
+          <t>53919</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>59723</t>
+          <t>60146</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>81762</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>100917</t>
+          <t>100577</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>129919</t>
+          <t>128923</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>53023</t>
+          <t>53282</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>75114</t>
+          <t>74725</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>103777</t>
+          <t>104517</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>130244</t>
+          <t>130384</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>164111</t>
+          <t>163422</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>196063</t>
+          <t>196890</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>116272</t>
+          <t>116759</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>141897</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>139747</t>
+          <t>140151</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>168891</t>
+          <t>168235</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>263785</t>
+          <t>264411</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>302733</t>
+          <t>302655</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>211610</t>
+          <t>202431</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>303189</t>
+          <t>305232</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>284318</t>
+          <t>289864</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>393181</t>
+          <t>393274</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>545353</t>
+          <t>534790</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>677308</t>
+          <t>679143</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>179675</t>
+          <t>187849</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>273694</t>
+          <t>271955</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>303510</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>420014</t>
+          <t>421723</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>535011</t>
+          <t>534577</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>673845</t>
+          <t>674359</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>411403</t>
+          <t>416339</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>594409</t>
+          <t>596112</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>564177</t>
+          <t>569538</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>763656</t>
+          <t>763516</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1063379</t>
+          <t>1066915</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1324425</t>
+          <t>1322797</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2325331</t>
+          <t>2323094</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2671353</t>
+          <t>2679751</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2104171</t>
+          <t>2108351</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2498472</t>
+          <t>2476478</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4490376</t>
+          <t>4490366</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4979233</t>
+          <t>4975461</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B3_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36857</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26886</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23892</t>
+          <t>28729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49515</t>
+          <t>45009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>51358</t>
+          <t>53607</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>36853</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>346705</t>
+          <t>352938</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318974</t>
+          <t>327145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366681</t>
+          <t>370874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>275588</t>
+          <t>315284</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>258105</t>
+          <t>293376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289138</t>
+          <t>329295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>622293</t>
+          <t>668222</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>634335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>646309</t>
+          <t>692993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22804</t>
+          <t>24327</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30454</t>
+          <t>34193</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46444</t>
+          <t>48217</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29414</t>
+          <t>31204</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44058</t>
+          <t>46131</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29884</t>
+          <t>32425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64500</t>
+          <t>64242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50550</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35595</t>
+          <t>45971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>83826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>61203</t>
+          <t>69785</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>54751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81436</t>
+          <t>87267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>131798</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81848</t>
+          <t>110594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138217</t>
+          <t>158578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>347189</t>
+          <t>387918</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>324638</t>
+          <t>365183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>365009</t>
+          <t>409112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>402580</t>
+          <t>378357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>375596</t>
+          <t>357756</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>445859</t>
+          <t>397926</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>749770</t>
+          <t>766275</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>716816</t>
+          <t>734953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>799072</t>
+          <t>793231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,102 +1863,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>42296</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51739</t>
+          <t>56254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>47505</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>38333</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>60491</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>89801</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>74537</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>109092</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>7,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>39211</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>30084</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49771</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>77893</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>62288</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>93515</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53710</t>
+          <t>58332</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35631</t>
+          <t>40249</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>30190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>51693</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>74557</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>59208</t>
+          <t>66850</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93281</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73514</t>
+          <t>83146</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58845</t>
+          <t>67728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91729</t>
+          <t>102072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>114703</t>
+          <t>129795</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99409</t>
+          <t>111704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129838</t>
+          <t>146720</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>188217</t>
+          <t>212941</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167679</t>
+          <t>187086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211800</t>
+          <t>237843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>384247</t>
+          <t>452729</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>361403</t>
+          <t>427588</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>404340</t>
+          <t>475077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>352922</t>
+          <t>404591</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>334945</t>
+          <t>384996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371475</t>
+          <t>424206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>737169</t>
+          <t>857320</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708007</t>
+          <t>827832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>765794</t>
+          <t>889026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1077837</t>
+          <t>1241988</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1077837</t>
+          <t>1241988</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1077837</t>
+          <t>1241988</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49986</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>43208</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76569</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>71125</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52854</t>
+          <t>58856</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84213</t>
+          <t>84182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>116377</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71801</t>
+          <t>106944</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150374</t>
+          <t>148258</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>57572</t>
+          <t>60694</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>47637</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88384</t>
+          <t>78191</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>86611</t>
+          <t>93932</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70494</t>
+          <t>79337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102697</t>
+          <t>108096</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>144183</t>
+          <t>154626</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89312</t>
+          <t>135343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179561</t>
+          <t>177535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>114710</t>
+          <t>122530</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>103170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>169559</t>
+          <t>141590</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>143155</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>119812</t>
+          <t>136391</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>162447</t>
+          <t>172178</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>257865</t>
+          <t>277049</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>160246</t>
+          <t>250915</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>316077</t>
+          <t>307314</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>665519</t>
+          <t>460623</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>566234</t>
+          <t>434082</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>788207</t>
+          <t>484189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>416341</t>
+          <t>416918</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>391346</t>
+          <t>396420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>465847</t>
+          <t>440519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1081860</t>
+          <t>877541</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>969011</t>
+          <t>842820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1274402</t>
+          <t>912369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>60227</t>
+          <t>65439</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48006</t>
+          <t>52193</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74503</t>
+          <t>81341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>77808</t>
+          <t>87289</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66204</t>
+          <t>74257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91290</t>
+          <t>100971</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>138035</t>
+          <t>152728</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121151</t>
+          <t>132588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>157851</t>
+          <t>173308</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>38213</t>
+          <t>39009</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27970</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>50670</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>88498</t>
+          <t>100120</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76384</t>
+          <t>86543</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102174</t>
+          <t>115182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>126711</t>
+          <t>139129</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111394</t>
+          <t>122098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145374</t>
+          <t>158017</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>118587</t>
+          <t>130554</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>102344</t>
+          <t>111766</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137194</t>
+          <t>150815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,27 +3262,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>133607</t>
+          <t>148434</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120686</t>
+          <t>133798</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149330</t>
+          <t>166472</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>252194</t>
+          <t>278988</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230074</t>
+          <t>254847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274915</t>
+          <t>305757</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>343178</t>
+          <t>373264</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>321644</t>
+          <t>350973</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>364865</t>
+          <t>396414</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>245653</t>
+          <t>272290</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>229466</t>
+          <t>252576</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>262574</t>
+          <t>290059</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>588831</t>
+          <t>645553</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>561381</t>
+          <t>615551</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>617809</t>
+          <t>673590</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1105770</t>
+          <t>1216397</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>43633</t>
+          <t>49641</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34435</t>
+          <t>39978</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>62193</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>65080</t>
+          <t>72271</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29410</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103731</t>
+          <t>83770</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>108713</t>
+          <t>121912</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58672</t>
+          <t>108022</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145698</t>
+          <t>138091</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30642</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>25522</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39885</t>
+          <t>44013</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>59505</t>
+          <t>65499</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95002</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>90147</t>
+          <t>98953</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47698</t>
+          <t>84781</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>119146</t>
+          <t>115009</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>85619</t>
+          <t>92200</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73021</t>
+          <t>78098</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>97850</t>
+          <t>105647</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>104862</t>
+          <t>112736</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>48378</t>
+          <t>99579</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>164516</t>
+          <t>127132</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>190481</t>
+          <t>204936</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105230</t>
+          <t>187336</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>250047</t>
+          <t>225653</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>208271</t>
+          <t>231785</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>194864</t>
+          <t>214824</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>224463</t>
+          <t>247022</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>378920</t>
+          <t>188659</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>253703</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>497798</t>
+          <t>203525</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>587191</t>
+          <t>420444</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>474333</t>
+          <t>395671</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>765408</t>
+          <t>443260</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,67 +4139,67 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>46758</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57674</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>94786</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>82428</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>109377</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t>20,4%</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>83736</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>72480</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>96903</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>130494</t>
+          <t>147103</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>116287</t>
+          <t>130209</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>146264</t>
+          <t>163706</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>43979</t>
+          <t>47851</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34551</t>
+          <t>37290</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>53919</t>
+          <t>58867</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>70673</t>
+          <t>77233</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>60146</t>
+          <t>66295</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>81362</t>
+          <t>90809</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>114652</t>
+          <t>125084</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>110691</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>128923</t>
+          <t>142451</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>63056</t>
+          <t>70506</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>53282</t>
+          <t>59464</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74725</t>
+          <t>83459</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>117049</t>
+          <t>124819</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>104517</t>
+          <t>111742</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>130384</t>
+          <t>138339</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>180105</t>
+          <t>195325</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>163422</t>
+          <t>177387</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>196890</t>
+          <t>214049</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>128966</t>
+          <t>139524</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>116759</t>
+          <t>124200</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>141897</t>
+          <t>153963</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>154373</t>
+          <t>167772</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>140151</t>
+          <t>153036</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>168235</t>
+          <t>182853</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>283339</t>
+          <t>307295</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>264411</t>
+          <t>284510</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>302655</t>
+          <t>327369</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>292352</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>202431</t>
+          <t>260031</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>305232</t>
+          <t>327369</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>354214</t>
+          <t>400453</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>289864</t>
+          <t>369211</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>393274</t>
+          <t>430684</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>620187</t>
+          <t>692806</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>534790</t>
+          <t>652314</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>679143</t>
+          <t>741865</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>234357</t>
+          <t>253081</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>187849</t>
+          <t>222458</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>271955</t>
+          <t>286683</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>380283</t>
+          <t>421648</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>316061</t>
+          <t>392528</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>421723</t>
+          <t>460424</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>614640</t>
+          <t>674729</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>534577</t>
+          <t>629565</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>674359</t>
+          <t>723269</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>533412</t>
+          <t>586479</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>416339</t>
+          <t>537915</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>596112</t>
+          <t>632500</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>698561</t>
+          <t>768165</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>569538</t>
+          <t>726975</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>763516</t>
+          <t>809251</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1231973</t>
+          <t>1354644</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1066915</t>
+          <t>1295799</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1420784</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2424076</t>
+          <t>2398780</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2323094</t>
+          <t>2334855</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2679751</t>
+          <t>2457467</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2226377</t>
+          <t>2143871</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2108351</t>
+          <t>2087037</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2476478</t>
+          <t>2194718</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4650453</t>
+          <t>4542651</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4490366</t>
+          <t>4457001</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4975461</t>
+          <t>4618111</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
